--- a/Lab work/Lab1_Kuntal Das.xlsx
+++ b/Lab work/Lab1_Kuntal Das.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/dfacd2f8281a70eb/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Anudip Foundation\Lab work\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="174" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{902975B2-E655-4D5B-846C-E39807B10613}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C231192D-6FF2-4575-A7E8-A09E129A913F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,9 +16,9 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="data">Sheet1!$A$1:$E$5</definedName>
+    <definedName name="mydata">Sheet1!$A$1:$K$9</definedName>
   </definedNames>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -33,6 +33,9 @@
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
